--- a/Data/Lambayeque/noticias_lambayeque_20261005_20261012.xlsx
+++ b/Data/Lambayeque/noticias_lambayeque_20261005_20261012.xlsx
@@ -466,14 +466,114 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fenómeno El Niño: el mar frente a Talara está caliente y temperatura llega a los 26.4 °C</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>De acuerdo con la información difundida, estas condiciones favorecen temperaturas del aire superiores a lo habitual, tanto durante el día como por la noche.
+Si persisten las anomalías positivas del mar, se prevé que las temperaturas del aire continúen elevadas durante las próximas semanas.
+Lea también: ¿Un aluvión como el ocurrido en Chile podría suceder en el Perú? Esto revela el Senamhi Sobre este tema, el especialista en Meteorología del Servicio Nacional de Meteorología e Hidrología (Senamhi), Nelson Quispe, explicó que, para evaluar el potencial de lluvias en la costa norte, es importante observar la temperatura absoluta del mar y no únicamente sus anomalías respecto de los valores habituales.
+Detalló que, cuando la temperatura superficial del mar supera los 26 grados Celsius, la atmósfera puede volverse más inestable y aumentar la posibilidad de formación de nubes que generen precipitaciones.
+Lea también: El Niño: previsiones del Senamhi dan cuenta de temperaturas de 40 grados en costa norte “Lo que debemos fijarnos ahora es el valor absoluto de la temperatura.
+Ese valor absoluto es que esté por encima de los 26 grados, 26.5 o 27 grados.
+Ese es el valor que debemos observar ahora”, manifestó.
+El especialista indicó que esta condición ya se registra en Tumbes, mientras que el calentamiento se extiende hacia el extremo norte de Piura; y agregó que cuando las temperaturas de alrededor de 26 grados abarquen Tumbes, Piura y Lambayeque, podrán comenzar a presentarse lluvias más generalizadas en esa zona.
+Senamhi advierte temperaturas de hasta 36 °C La Dirección Zonal 01 del Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi) emitió el Aviso Meteorológico Regional N.° 181 por el incremento de la temperatura diurna en la costa y sierra norte, vigente del 10 al 13 de octubre.
+El pronóstico contempla temperaturas máximas de entre 25 °C y 36 °C en la costa norte, y de entre 22 °C y 33 °C en la sierra norte.
+También se prevé escasa nubosidad hacia el mediodía, condición que favorecerá el aumento de la radiación ultravioleta (UV), además de ráfagas de viento cercanas a los 40 kilómetros por hora, principalmente por la tarde.
+No se descartan lluvias dispersas en la costa norte.
+Prevén lluvias y lloviznas en la región El Senamhi también publicó el Aviso Meteorológico Regional N.° 182 por lloviznas en la costa norte, previsto para el 13 y 14 de octubre.
+El evento estará acompañado por un incremento de la velocidad del viento y presencia de niebla y neblina en sectores cercanos al litoral, principalmente durante la noche, la madrugada y las primeras horas de la mañana.
+A estas condiciones se suma el Aviso Meteorológico Regional N.° 183, que pronostica lluvias de ligera a moderada intensidad en la costa y sierra norte entre el 12 y el 13 de octubre, acompañadas de ráfagas de viento cercanas a los 40 kilómetros por hora.
+Los acumulados previstos son de alrededor de 17 milímetros por día en la costa norte y de entre 8 y 17 milímetros por día en la sierra norte.
+Las condiciones previstas combinan temperaturas elevadas, alta radiación UV, viento y precipitaciones.
+La evolución del tiempo dependerá de la persistencia de estos factores durante los próximos días.
+Más en Andina:</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-fenomeno-nino-mar-frente-a-talara-esta-caliente-y-temperatura-llega-a-los-264-°c-1095606.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Resultados ONPE en región Lambayeque al 98.270 %: aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>El domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios iniciaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación en región Lambayeque según la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/resultados-en-lambayeque-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gobierno fortalece calidad del agua en beneficio de más de dos millones de peruanos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Con esta transferencia de partidas, autorizada mediante el Decreto Supremo 174-2026-EF, se podrá financiar la adquisición de insumos esenciales para la cloración de alrededor de 13,800 sistemas de agua potable (SAP) en favor de más de dos millones de pobladores de las zonas rurales del país , señaló el MVCS.
+Precisó que los recursos serán destinados a la adquisición de 256,889 kilos de hipoclorito de calcio y más de 2 millones 651,712 unidades de reactivos DPD, insumos indispensables para las actividades de limpieza, desinfección, monitoreo y adecuada cloración de los sistemas de agua potable, garantizando la protección de la salud y el bienestar de la población rural.
+Municipalidades beneficiarias Las municipalidades beneficiarias se encuentran en Amazonas, Áncash, Apurímac, Arequipa, Ayacucho, Cajamarca, Cusco, Huancavelica, Huánuco, Junín, La Libertad, Lambayeque, Lima, Loreto, Moquegua, Pasco, Piura, Puno, San Martín, Tacna y Ucayali.
+En este proceso el PNSR brinda acompañamiento técnico a los gobiernos locales para la incorporación de los recursos transferidos en su Presupuesto Institucional Modificado (PIM), a fin de facilitar el inicio de los respectivos procesos de adquisición y garantizar la disponibilidad oportuna de estos insumos estratégicos.
+El Ministerio de Vivienda indicó que, con esta intervención, se fortalece la gestión de los servicios de agua potable en el ámbito rural y contribuye a la sostenibilidad de los sistemas, al favorecer la disponibilidad de insumos necesarios para su adecuada operación, mantenimiento y control de la calidad del agua.
+Más en Andina: ???? Perú crecería 3.2% en 2026, según el Banco Mundial.
+La inversión privada en minería e infraestructura, la recuperación del consumo y la demanda global de cobre serían claves para la expansión económica.
+?? https://t.co/goSIyt3I9v?? William Rios Rosales https://t.co/gKM1UjIxKK (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 12, 2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-gobierno-fortalece-calidad-del-agua-beneficio-mas-dos-millones-peruanos-1095602.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
         <v>46306</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Clausuran establecimientos clandestinos de apuestas deportivas en Lambayeque y Huánuco</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Precisó que las intervenciones estuvieron a cargo de la Dirección General de Juegos de Casino y Máquinas Tragamonedas del Mincetur, con el apoyo de la Policía Nacional del Perú, y forman parte de las acciones para combatir la informalidad, proteger a los usuarios y garantizar que estas actividades se desarrollen conforme a la legislación vigente.
 Mincetur indicó que en Chiclayo, región Lambayeque, se intervinieron tres establecimientos clandestinos, donde se incautaron 32 máquinas tragamonedas.
@@ -486,27 +586,62 @@
 Más en Andina:</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-clausuran-establecimientos-clandestinos-apuestas-deportivas-lambayeque-y-huanuco-1095521.aspx</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
         <v>46306</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ministerio de Comercio Exterior y Turismo intensifica operativos contra el juego ilegal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Las intervenciones estuvieron a cargo de la Dirección General de Juegos de Casino y Máquinas Tragamonedas del Mincetur, con el apoyo de la Policía Nacional del Perú, y forman parte de las acciones para combatir la informalidad, proteger a los usuarios y garantizar que estas actividades se desarrollen conforme a la legislación vigente.
+En Chiclayo, región Lambayeque, se intervinieron tres establecimientos clandestinos, donde se incautaron 32 máquinas tragamonedas.
+Asimismo, en el distrito de José Luis de Crespo y Castillo, provincia de Leoncio Prado, región Huánuco, se intervino tres establecimientos decomisando 12 máquinas tragamonedas y 41 equipos informáticos utilizados para realizar apuestas deportivas en línea sin autorización.
+Durante las acciones de fiscalización también se detectaron máquinas tragamonedas destinadas a menores de edad, una práctica expresamente prohibida por la legislación peruana debido a los riesgos que representan para niños y adolescentes.
+Los operativos se ejecutaron en el marco de las leyes N.° 27153, que regula la explotación de juegos de casino y máquinas tragamonedas; N.° 31557, que establece el marco legal para los juegos y apuestas deportivas a distancia; y N.° 29149, que sanciona las actividades vinculadas con máquinas tragamonedas dirigidas a menores de edad.
+Establecimientos ilegales cerrados Como resultado de las acciones de control y fiscalización, el Mincetur ha dispuesto el cierre de 19 locales de apuestas deportivas ilegales y 14 salas clandestinas de máquinas tragamonedas en lo que va de 2026.
+El sector recordó que quienes promuevan, organicen o participen en actividades de juego ilegal pueden enfrentar penas privativas de libertad, además de las sanciones administrativas y económicas correspondientes, según la infracción cometida y la normativa aplicable.
+El Mincetur exhortó a la ciudadanía a denunciar actividades clandestinas relacionadas con apuestas deportivas, casinos o máquinas tragamonedas a través del teléfono (01) 513-6113 o del correo electrónico denuncias_casinos@mincetur.gob.pe.
+Para culminar, el Mincetur reafirma su compromiso con el juego responsable, fortaleciendo las acciones de fiscalización y el desarrollo de actividades autorizadas y seguras.
+Más en Andina: ¡Mercado potencial! ???? Japón podría consumir más anguila peruana tras lograr certificación MSC.
+Perú es primer país en lograr dicha certificación https://t.co/pfQoJ9kdU7Por: ?? Miguel De la Vega https://t.co/OFdQbzfQn7 (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) September 28, 2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-ministerio-comercio-exterior-y-turismo-intensifica-operativos-contra-juego-ilegal-1095518.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>¡León XIV en Chiclayo! Panaderos de Monsefú elaboran panes artísticos en homenaje al papa</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Hildebrando Bonilla, presidente de la Asociación de Panificadores Industriales de Monsefú , explicó en diálogo con la Agencia Andina que estas piezas especiales forman parte del homenaje que los panaderos de esta localidad preparan para el pontífice, quien mantuvo vínculos pastorales con Chiclayo cuando se desempeñaba como obispo.
 Las creaciones, elaboradas íntegramente a mano con masa de pan comestible , alcanzan aproximadamente 60 centímetros de altura y requieren ocho horas de trabajo, debido al cuidado de los detalles y a la complejidad de sus diseños.
@@ -523,27 +658,27 @@
 Más en Andina: Un temblor de magnitud 5.1, con una profundidad de 57 kilómetros se registró en la mañana de hoy domingo 11 de octubre en la región Arequipa, informó el Centro Sismológico Nacional.??https://t.co/vNqIUxMt2T https://t.co/ELS8BgIzXC (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 11, 2026</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-leon-xiv-chiclayo-panaderos-monsefu-elaboran-panes-artisticos-homenaje-al-papa-1095496.aspx</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
         <v>46306</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Minam y gobiernos regionales impulsan acciones para conservar la biodiversidad</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Así lo informó el Minam que precisó que en la cita participaron representantes de Arequipa, Ayacucho, Cajamarca, Áncash, Lambayeque, Amazonas, Apurímac, Ica, Madre de Dios, Puno y Piura , entre otras regiones.
 Durante el encuentro se abordó la articulación de las prioridades regionales con la Estrategia Nacional de Diversidad Biológica al 2050 y su Plan de Acción al 2030.
@@ -555,148 +690,27 @@
 Más en Andina: Hace más de 1,400 años aproximadamente, la muerte repentina de un infante miembro de la élite mochica, generó un importante ritual funerario al pie de la huaca de la Luna, uno de los templos religiosos más importantes de esta sociedad prehispánica, que se asentó en el valle del actual distrito de Moche, en la provincia de Trujillo.??https://t.co/GeKo8fnBPE (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 11, 2026</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-minam-y-gobiernos-regionales-impulsan-acciones-para-conservar-biodiversidad-1095488.aspx</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>46306</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Resultados ONPE en región Lambayeque al 98.270 %: conoce aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>El domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios iniciaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación en región Lambayeque según la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/resultados-en-lambayeque-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>46306</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>¿Un aluvión como el ocurrido en Chile podría suceder en el Perú? Esto revela el Senamhi</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>El especialista en Meteorología del Servicio Nacional de Meteorología e Hidrología (Senamhi), Nelson Quispe, afirma que el Perú podría registrar episodios de lluvias intensas, huaicos y activación de quebradas similares a los ocurridos recientemente en Chile, especialmente durante el próximo verano, debido a las condiciones asociadas al fenómeno El Niño y al calentamiento de la temperatura superficial del mar.
-Lea también: Enfen: lluvias intensas serán más frecuentes desde octubre por El Niño extraordinario En declaraciones a la Agencia Andina, Quispe explicó que las precipitaciones de corta duración y gran intensidad pueden desencadenar emergencias en distintas regiones del país, incluso en escenarios en los que se proyecta un déficit de lluvias para determinadas zonas.
-“Tenemos historia de esas condiciones que sucedieron en las zonas de Chile, así que no nos extrañaría que podría suceder, especialmente en el verano, donde las lluvias son mayores.
-Podría darse condiciones de lluvia intensa y la activación de las quebradas”, aseveró.
-El especialista del Senamhi recordó que el Perú ha experimentado episodios destructivos de precipitaciones y huaicos, como los registrados en Mirave, en Tacna en febrero de 2019, en Secocha, Arequipa, en febrero de 2023, así como las lluvias intensas que afectaron Chosica en abril de 2013.
-Estos antecedentes, indicó, evidencian que una precipitación concentrada en un periodo breve puede ocasionar graves daños, desbordes y pérdidas humanas, por lo que resulta importante prestar atención no solo a los acumulados mensuales de lluvia, sino también a su intensidad y duración.
-Lluvias intensas en Chile Respecto a las recientes emergencias registradas en Chile , el especialista explicó que estas se produjeron luego de varios días consecutivos de precipitaciones, a los que se sumó un episodio de lluvia particularmente intensa.
-Según lo señalado por Quispe, en aproximadamente 20 minutos se acumularon entre 20 y 22 milímetros de lluvia, situación que favoreció la activación de quebradas y la ocurrencia de aluviones.
-El especialista sostuvo que, durante un evento El Niño, el calentamiento puede intensificar las condiciones atmosféricas favorables para las precipitaciones, aunque la ocurrencia de estos episodios también depende de otros factores meteorológicos.
-En ese sentido, precisó que no se trata necesariamente de un fenómeno meteorológico aislado, sino de condiciones que pueden verse potenciadas por el escenario climático que atraviesa la región.
-Temperatura del mar supera los 26 grados en Tumbes Quispe explicó que, para evaluar el potencial de lluvias en la costa norte, es importante observar la temperatura absoluta del mar y no únicamente sus anomalías respecto de los valores habituales.
-Detalló que, cuando la temperatura superficial del mar supera los 26 grados Celsius, la atmósfera puede volverse más inestable y aumentar la posibilidad de formación de nubes que generen precipitaciones.
-“Lo que debemos fijarnos ahora es el valor absoluto de la temperatura.
-Ese valor absoluto es que esté por encima de los 26 grados, 26,5 o 27 grados.
-Ese es el valor que debemos observar ahora”, manifestó.
-El especialista indicó que esta condición ya se registra en Tumbes, mientras que el calentamiento se extiende hacia el extremo norte de Piura.
-Sin embargo, aclaró que todavía no se presenta de manera generalizada en toda la costa norte.
-Explicó que, cuando las temperaturas de alrededor de 26 grados abarquen Tumbes, Piura y Lambayeque, podrán comenzar a presentarse lluvias más generalizadas en esa zona.
-Tumbes podría registrar lluvias de hasta 70 milímetros Para los próximos días, el Senamhi espera precipitaciones de moderada a fuerte intensidad en Tumbes, con acumulados de entre 30 y 40 milímetros en las zonas bajas.
-En las áreas próximas a la frontera con Ecuador, los valores podrían superar los 70 milímetros, precisó Quispe.
-El especialista explicó que las lluvias registradas en las cabeceras de cuenca pueden provocar incrementos rápidos y pronunciados del caudal de los ríos, como ocurrió recientemente en la región.
-Asimismo, indicó que durante el verano los acumulados de lluvia en Tumbes podrían superar los 100 milímetros y alcanzar incluso los 150 milímetros en determinados episodios.
-Estos valores pueden considerarse precipitaciones fuertes o extremas, dependiendo de las características climatológicas de cada localidad, puntualizó.
-Quispe remarcó que la intensidad de una lluvia debe evaluarse de acuerdo con las condiciones habituales de cada región.
-Así, una precipitación de pocos milímetros puede representar un evento fuerte en sectores de la costa central, mientras que en otras zonas se requieren acumulados mayores para alcanzar esa categoría.
-No se descartan lluvias focalizadas en el sur El especialista del Senamhi advirtió que podrían presentarse precipitaciones intensas y localizadas en sectores de Tacna, Moquegua y Arequipa, pese a que para algunas zonas del sur se prevé un escenario de déficit hídrico relacionado con la interacción del fenómeno El Niño Costero y El Niño global.
-Explicó que una sola lluvia intensa puede generar huaicos y otros daños, aunque el balance mensual termine mostrando precipitaciones por debajo de lo normal.
-“En una zona de la parte sur de Tacna, Moquegua, puede haber una lluvia intensa, una sola lluvia que te puede generar todo esto y luego el día siguiente se seca todo y mantiene deficiente.
-Y cuando sacas el promedio de todo, el mes va a ser deficiente, pero una sola lluvia te puede generar gran cosa”, señaló.
-Añadió que la posibilidad de precipitaciones es mayor en la zona centro-norte del país, mientras que en la costa centro-sur es menor debido, entre otros factores, a la interacción con el fenómeno El Niño global.
-No obstante, subrayó que ello no significa que se descarten episodios puntuales de lluvia.
-Lluvias más consecutivas desde mediados de noviembre Quispe precisó que el periodo de lluvias ya debería estar manifestándose en distintas zonas del país, por lo que consideró que la principal preocupación debe centrarse en determinar cuándo se producirán las precipitaciones y qué intensidad alcanzarán, en lugar de enfocarse únicamente en si la temporada se adelanta o se retrasa.
-Indicó que la atmósfera todavía no se encuentra suficientemente acoplada al calentamiento del mar, condición que favorecería lluvias más frecuentes y consecutivas.
-En ese contexto, estimó que desde mediados de noviembre podría observarse un mayor acoplamiento entre ambos componentes, lo que facilitaría la ocurrencia de precipitaciones más persistentes.
-Para octubre, en cambio, se esperan episodios aislados de lluvia, mientras que el incremento del calentamiento del mar durante noviembre contribuiría a generar condiciones más favorables para las precipitaciones.
-El especialista recomendó mantener la atención en la evolución de las lluvias y en los posibles incrementos repentinos de los caudales, debido a que los episodios de corta duración pueden generar emergencias incluso en zonas donde el pronóstico estacional apunta a condiciones deficitarias.
-Más en Andina: ¡Hallazgo en Trujillo! Descubren tumba de infante de élite mochica en la huaca de la Luna https://t.co/8J3T2uL3ME https://t.co/dnQUuFSeKN (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 9, 2026</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-un-aluvion-como-ocurrido-chile-podria-suceder-el-peru-esto-revela-senamhi-1095328.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>46306</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ministerio de Comercio Exterior y Turismo intensifica operativos contra el juego ilegal</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Las intervenciones estuvieron a cargo de la Dirección General de Juegos de Casino y Máquinas Tragamonedas del Mincetur, con el apoyo de la Policía Nacional del Perú, y forman parte de las acciones para combatir la informalidad, proteger a los usuarios y garantizar que estas actividades se desarrollen conforme a la legislación vigente.
-En Chiclayo, región Lambayeque, se intervinieron tres establecimientos clandestinos, donde se incautaron 32 máquinas tragamonedas.
-Asimismo, en el distrito de José Luis de Crespo y Castillo, provincia de Leoncio Prado, región Huánuco, se intervino tres establecimientos decomisando 12 máquinas tragamonedas y 41 equipos informáticos utilizados para realizar apuestas deportivas en línea sin autorización.
-Durante las acciones de fiscalización también se detectaron máquinas tragamonedas destinadas a menores de edad, una práctica expresamente prohibida por la legislación peruana debido a los riesgos que representan para niños y adolescentes.
-Los operativos se ejecutaron en el marco de las leyes N.° 27153, que regula la explotación de juegos de casino y máquinas tragamonedas; N.° 31557, que establece el marco legal para los juegos y apuestas deportivas a distancia; y N.° 29149, que sanciona las actividades vinculadas con máquinas tragamonedas dirigidas a menores de edad.
-Establecimientos ilegales cerrados Como resultado de las acciones de control y fiscalización, el Mincetur ha dispuesto el cierre de 19 locales de apuestas deportivas ilegales y 14 salas clandestinas de máquinas tragamonedas en lo que va de 2026.
-El sector recordó que quienes promuevan, organicen o participen en actividades de juego ilegal pueden enfrentar penas privativas de libertad, además de las sanciones administrativas y económicas correspondientes, según la infracción cometida y la normativa aplicable.
-El Mincetur exhortó a la ciudadanía a denunciar actividades clandestinas relacionadas con apuestas deportivas, casinos o máquinas tragamonedas a través del teléfono (01) 513-6113 o del correo electrónico denuncias_casinos@mincetur.gob.pe.
-Para culminar, el Mincetur reafirma su compromiso con el juego responsable, fortaleciendo las acciones de fiscalización y el desarrollo de actividades autorizadas y seguras.
-Más en Andina: ¡Mercado potencial! ???? Japón podría consumir más anguila peruana tras lograr certificación MSC.
-Perú es primer país en lograr dicha certificación https://t.co/pfQoJ9kdU7Por: ?? Miguel De la Vega https://t.co/OFdQbzfQn7 (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) September 28, 2026</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-ministerio-comercio-exterior-y-turismo-intensifica-operativos-contra-juego-ilegal-1095518.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
         <v>46305</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Presidenta Fujimori: "No vamos a poner excusas, vamos a traer decisión y resultados"</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>“Cuando llegamos al gobierno hemos encontrado miles de obras paralizadas.
 Como la de ustedes, efectivamente.
@@ -750,27 +764,27 @@
 ?? https://t.co/uELPoHXWrO (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 10, 2026</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-presidenta-fujimori-no-vamos-a-poner-excusas-vamos-a-traer-decision-y-resultados-1095434.aspx</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
         <v>46305</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>ExpoAmazónica Ucayali 2026: 41 expositores representarán a región San Martín</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>La comitiva fue organizada por el Gobierno Regional de San Martín, a través del proyecto Oferta Exportable de la Gerencia Regional de Desarrollo Económico.
 Está conformada por empresas, asociaciones, cooperativas y emprendimientos de distintas provincias, cuya oferta abarca café, cacao y chocolate, miel, coco, artesanía, cosmética natural, charcutería, licores, lácteos, sal, palmito, confitería, aceites naturales y arroz.
@@ -782,27 +796,27 @@
 La presencia de San Martín en la ExpoAmazónica Ucayali 2026 forma parte de las acciones de promoción comercial que impulsa el Gobierno Regional para visibilizar la producción local y facilitar la articulación empresarial.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-expoamazonica-ucayali-2026-41-expositores-representaran-a-region-san-martin-1095428.aspx</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
         <v>46305</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Chiclayo proyecta recibir a 1.5 millones de visitantes por el papa León XIV</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>En este escenario, se inauguró en la explanada de la agencia del Banco de la Nación de Chiclayo la feria artesanal “Tradición Viva”, que busca convertirse en una vitrina del talento, la identidad cultural y las tradiciones de Lambayeque, brindando oportunidades comerciales a las artesanas y promoviendo la venta de productos elaborados por manos peruanas ante la llegada de miles de peregrinos nacionales y extranjeros.
 Uno de los atractivos será la réplica de la estola que será donada al Santo Padre, una muestra de creatividad y trabajo artesanal que refleja la identidad cultural de la región.
@@ -829,27 +843,27 @@
 El desafío será convertir esta afluencia extraordinaria en beneficios sostenibles para los emprendedores y las familias de la región.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-chiclayo-proyecta-recibir-a-15-millones-visitantes-por-papa-leon-xiv-1095414.aspx</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
         <v>46305</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>El Niño: ANIN invierte S/ 1.4 millones para prevenir desbordes del río La Leche</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>La intervención abarca cerca de dos kilómetros de cauce, demanda una inversión superior a S/ 1.4 millones y tiene un plazo aproximado de 50 días.
 Para ejecutarla, la ANIN movilizó equipos de su propia flota: una excavadora, un cargador frontal, cuatro volquetes y dos tractores, lo que le permite intervenir de forma directa y oportuna.
@@ -861,52 +875,150 @@
 Estas acciones se realizan gracias a un convenio de cooperación interinstitucional, el Gobierno Regional de Lambayeque proporciona la maquinaria necesaria y la ANIN suministra el combustible para mantener las labores de limpieza y descolmatación del cauce, así como la conformación de un dique con material de la zona, de acuerdo con la ficha técnica del sector.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-el-nino-anin-invierte-s-14-millones-para-prevenir-desbordes-del-rio-leche-1095397.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Lambayeque: escultor prepara una estatua de más de dos metros del papa León XIV en Zaña</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>A pocas semanas de la llegada del papa León XIV al Perú, continúan los preparativos en la región Lambayeque para rendir homenaje al sumo pontífice. En el distrito de Zaña se instalará una escultura de más de dos metros de altura, elaborada por el artista Jaime Cachay, quien prevé culminar la obra a fines de octubre. “Hemos empezado ya, aproximadamente hace un mes, con la confección de la escultura y por lo menos estamos acabando a fines de octubre y estaremos entregando la escultura. El material que se está utilizando es fibra de vidrio con resinas, con triple capa de fibra de vidrio resistente a la intemperie y al golpe”, declaró el escultor a TV Perú. La estructura será trasladada desde el taller de Cachay, ubicado en Monsefú, hasta el distrito de Zaña. La obra busca rendir homenaje al papa León XIV, quien es recordado en Lambayeque por su labor pastoral como obispo de Chiclayo entre 2013 y 2023. No es la primera escultura del pontífice elaborada por Cachay. El año pasado, el artista, natural de Monsefú y conocido por sus obras religiosas y monumentales, estuvo a cargo de la estatua de 2,60 metros de altura instalada en el distrito de Pimentel, en la provincia de Chiclayo. La escultura fue develada el 17 de octubre, durante las actividades por el 105.º aniversario de Pimentel. La obra, fabricada íntegramente con fibra de vidrio y colocada sobre un atril de madera, se encuentra en el segundo malecón del balneario, a pocos metros del tradicional muelle. Pimentel forma parte de la Ruta Turística Caminos del Papa León XIV, un recorrido que comprende lugares vinculados con Robert Prevost y busca promover el turismo religioso en la región. Por su parte, en la ciudad de Chiclayo también se encuentra en la etapa final la construcción de una escultura monumental del papa León XIV, de cinco metros de altura, montada sobre un pedestal de dos metros. El proyecto está a cargo del escultor chiclayano Juan Carlos Ñañaque Torres y también utiliza fibra de vidrio como material principal.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/peru/lambayeque/papa-leon-xiv-jaime-cachay-escultor-peruano-prepara-una-estatua-de-mas-de-dos-metros-del-santo-padre-en-zana-apuesplan-ultimas-noticia/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Lambayeque: escultor prepara una estatua de más de dos metros del papa León XIV en Zaña</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A pocas semanas de la llegada del papa León XIV al Perú, continúan los preparativos en la región Lambayeque para rendir homenaje al sumo pontífice. En el distrito de Zaña se instalará una escultura de más de dos metros de altura, elaborada por el artista Jaime Cachay, quien prevé culminar la obra a fines de octubre. “Hemos empezado ya, aproximadamente hace un mes, con la confección de la escultura y por lo menos estamos acabando a fines de octubre y estaremos entregando la escultura. El material que se está utilizando es fibra de vidrio con resinas, con triple capa de fibra de vidrio resistente a la intemperie y al golpe”, declaró el escultor a TV Perú. La estructura será trasladada desde el taller de Cachay, ubicado en Monsefú, hasta el distrito de Zaña. La obra busca rendir homenaje al papa León XIV, quien es recordado en Lambayeque por su labor pastoral como obispo de Chiclayo entre 2013 y 2023. No es la primera escultura del pontífice elaborada por Cachay. El año pasado, el artista, natural de Monsefú y conocido por sus obras religiosas y monumentales, estuvo a cargo de la estatua de 2,60 metros de altura instalada en el distrito de Pimentel, en la provincia de Chiclayo. La escultura fue develada el 17 de octubre, durante las actividades por el 105.º aniversario de Pimentel. La obra, fabricada íntegramente con fibra de vidrio y colocada sobre un atril de madera, se encuentra en el segundo malecón del balneario, a pocos metros del tradicional muelle. Pimentel forma parte de la Ruta Turística Caminos del Papa León XIV, un recorrido que comprende lugares vinculados con Robert Prevost y busca promover el turismo religioso en la región. Por su parte, en la ciudad de Chiclayo también se encuentra en la etapa final la construcción de una escultura monumental del papa León XIV, de cinco metros de altura, montada sobre un pedestal de dos metros. El proyecto está a cargo del escultor chiclayano Juan Carlos Ñañaque Torres y también utiliza fibra de vidrio como material principal.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/peru/lambayeque/papa-leon-xiv-jaime-cachay-escultor-peruano-prepara-una-estatua-de-mas-de-dos-metros-del-santo-padre-en-zana-apuesplan-ultimas-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Senado: Comisión de Constitución sesiona hoy para debatir facultades legislativas</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Con ese propósito, el presidente de dicha comisión, Carlos Mesía Ramírez (Fuerza Popular) citó mediante un oficio a los miembros titulares y suplentes de dicho grupo de trabajo para que asistan a esta reunión que se realizará en la sala Miguel Grau, del Palacio Legislativo.
+Lee también: Presidenta entregó títulos en Lambayeque y dijo que brindan seguridad jurídica a familias La sesión será la continuación de la reunión convocada el viernes y en la que se presentó el presidente del Consejo de Ministros, Luis Galarreta , y los ministros de Desarrollo Agrario y Riego, Marco Vinelli, y de la Producción, Juan Carlos Requejo.
+El titular de la Presidencia del Consejo de Ministros (PCM) reiteró durante su presentación en la necesidad de que el Congreso otorgue mayores facultades legislativas que las aprobadas en la propuesta legislativa de la Cámara Baja, mediante la cual se otorga facultades al Ejecutivo en materias de seguridad ciudadana y fenómeno El Niño por un periodo de 90 días.
+De acuerdo con el premier Galarreta son insuficientes las facultades aprobadas en la Cámara de Diputados, incluso en materia de seguridad ciudadana y fenómeno El Niño, ya que en cuanto a seguridad se requiere una mayor inteligencia operativa para combatir a las bandas criminales.
+Al término de esta sesión, el presidente de la Comisión de Constitución, señaló que están pendientes la presentación de los ministros de Justicia y Derechos Humanos , Ernesto Álvarez, y de Vivienda, Construcción y Saneamiento , Mauricio Arnillas.
+De este modo, el Senado continuará con el debate de las facultades legislativas planteadas por el Ejecutivo el 29 de agosto pasado y que la Cámara de Diputados aprobó solo 20 de los 66 puntos planteados inicialmente.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-senado-comision-constitucion-sesiona-hoy-para-debatir-facultades-legislativas-1095346.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Agro Rural interviene 49 puntos críticos para proteger áreas agrícolas en la región Lima</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Los trabajos, que se vienen ejecutando con una inversión de S/ 29.3 millones, protegerán 791 hectáreas de cultivos y beneficiarán a 1,874 familias productoras.
+Estos trabajos incluyen la limpieza, descolmatación y encimado de bordos en 44 kilómetros de cauces de ríos y quebradas, entre ellos las cuencas de los ríos Supe, Chillón y Huaral y la quebrada de Gorgor.
+Asimismo, se interviene en otros sectores ubicados en las provincias de Canta, Cajatambo, Barranca, Oyón, Huarochirí y Yauyos, “donde se han reconocido puntos que requieren atención inmediata”, explicó Agro Rural, en una nota de prensa.
+[Lea también: San Martín: sentencia judicial refuerza la protección de bosques amazónicos ] Trabajos culminados En el marco de las actividades de preparación y respuesta, el director ejecutivo de Agro Rural, Oscar Olivera Cusilayme, inspeccionó los trabajos ejecutados y culminados en los sectores Macas I y Macas II (Santa Rosa de Quives, Canta), verificando en campo las acciones en estos puntos críticos.
+En Macas II, los trabajos finalizaron al 100 % la segunda quincena de setiembre, mientras que, en Macas I culminaron los primeros días de octubre.
+“La intervención comprendió la limpieza y descolmatación de 1,730 metros de cauce y conformación de 3,460 metros de bordos en ambas márgenes del río Chillón”, detalló la institución.
+Estos trabajos benefician a por lo menos 50 familias productoras locales y protegen aproximadamente 100 hectáreas de cultivos, principalmente hortalizas –como col y brócoli– y también maíz.
+“Además, esta es la mejor evidencia de que estamos actuando y dando respuesta de manera efectiva, antes de que llegue la emergencia” por El Niño, aseguró la autoridad del programa del Midagri.
+[Lea también: El Niño: ¿Cómo enfrentaron las antiguas culturas del Perú los impactos de este fenómeno? ] Más intervenciones de Agro Rural Como parte de este recorrido, Olivera Cusilayme también participó en el inicio de dos nuevos servicios de intervención en otros puntos críticos de esta misma región.
+El primero comprende igualmente limpieza, descolmatación y encimado de bordos en diversas zonas de las provincias de Canta, Barranca, Cajatambo y Oyón, labores que se efectuarán con una inversión de S/ 14.09 millones y tendrán un plazo de ejecución de 45 días calendario.
+Al mismo tiempo, comenzaron las intervenciones en sectores como Autisha y Pongo (distrito de Huachupampa), Tambo de Viso (San Mateo), Corcona (Santa Cruz de Cocachacra), entre otros de las provincias de Huarochirí y Yauyos, con una inversión de S/ 5.84 millones y un plazo de 30 días.
+“Nuestra institución continuará ampliando progresivamente su presencia en diversos ámbitos, atendiendo localidades priorizadas ante posibles impactos que podrían comprometer seriamente los medios de vida de los productores familiares”, expresó Olivera.
+Todas estas labores se realizan en cumplimiento del Decreto Supremo N°164-2026-EF que dispone medidas frente a posibles impactos asociados a las intensas precipitaciones por El Niño.
+[Lea también: Fenómeno El Niño: supervisan los trabajos de descolmatación en punto crítico de Lambayeque ] Más en Andina: ?? Los pequeños productores agrarios cuentan con el Seguro Agrícola Catastrófico para afrontar pérdidas ocasionadas por eventos climáticos.
+El Midagri informó que este seguro es gratuito y ofrece una cobertura de hasta S/ 1,000 por hectárea.
+Más información ?? https://t.co/zSIv3qczUr (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 9, 2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-agro-rural-interviene-49-puntos-criticos-para-proteger-areas-agricolas-la-region-lima-1095333.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Presidenta Fujimori participa en entrega de títulos de propiedad en región Lambayeque</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A dicha zona de la región norteña, la mandataria llegó acompañada por el ministro de Vivienda, Construcción y Saneamiento, Mauricio Arnillas.
+La jefa del Estado personalmente entregó dos títulos de propiedad a las familias beneficiarias ; así como recibió el saludo de la población.
+También acompañan a la presidenta Fujimori, la directora ejecutiva de Cofopri, Cecilia Castro ; así como autoridades municipales y distritales.
+En la ceremonia que se desarrollará en breve, se entregarán más de 2,000 títulos de propiedad .</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-presidenta-fujimori-participa-entrega-titulos-propiedad-region-lambayeque-1095335.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Presidenta entregó títulos en Lambayeque y dijo que brindan seguridad jurídica a familias</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>La ceremonia se realizó en la explanada de este centro poblado ubicado en el distrito de Picsi.
 Los títulos de propiedad para la región Lambayeque benefician a más de 8,400 pobladores de la provincia de Chiclayo , Lambayeque y Ferreñafe.
@@ -938,127 +1050,57 @@
 Posteriormente, la mandataria realizó visitas inopinadas a la Institución Educativa Inicial N.° 133 y a la Institución Educativa N.° 1134 Capote Otto Zoeger Silva , donde verificó las condiciones en que operan ambos planteles y recogió directamente las inquietudes y necesidades de docentes y estudiantes.</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-presidenta-entrego-titulos-lambayeque-y-dijo-brindan-seguridad-juridica-a-familias-1095342.aspx</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Perú expresa solidaridad con pueblo y Gobierno de Panamá tras fuerte sismo</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>El Gobierno del Perú expresa su solidaridad al pueblo y al Gobierno de la República de Panamá, a consecuencia del fuerte sismo ocurrido en la fecha en ese hermano país.En estos momentos difíciles, el Perú formula sus sentidos votos por la pronta recuperación de las personas y zonas afectadas.
-— Cancillería Perú???? (@CancilleriaPeru) October 9, 2026 A través de un comunicado, el Ministerio de Relaciones Exteriores señaló que “el Perú formula sus sentidos votos por la pronta recuperación de las personas y zonas afectadas” .
-Monitoreo En ese sentido, la Cancillería informó que monitorea la situación y mantiene su atención a cualquier requerimiento de asistencia que pudieran presentar los ciudadanos peruanos en Panamá.
-Para ello, los connacionales pueden comunicarse con el Consulado General del Perú en Panamá a través del número +507 6866 2294 o del correo electrónico info@conperpanama.com.
-Lea también: Terremoto de magnitud 7.7 sacude Panamá y causa daños en edificios De acuerdo con el Servicio Geológico de Estados Unidos (USGS), el terremoto alcanzó una magnitud de 7.7 y tuvo su epicentro a 10 kilómetros de Pitaloza Arriba, en la provincia de Herrera, en el centro sur de Panamá.
-El movimiento telúrico se registró a las 12:56 (hora local) y fue sentido durante aproximadamente un minuto en Ciudad de Panamá, donde miles de personas salieron de los edificios por temor.
-Se reportó, asimismo, el colapso de algunos edificios en el centro del país.
-El Instituto de Geociencias de Panamá también informó sobre más de una decena de réplicas importantes, algunas de magnitud 6.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-peru-expresa-solidaridad-pueblo-y-gobierno-panama-tras-fuerte-sismo-1095326.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Diez postulantes al cargo de jefe de la ONPE rindieron evaluación de conocimientos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>?? ? Imágenes de los momentos previos al examen de conocimientos del concurso público para la selección y nombramiento del jefe de la ONPE (convocatoria n.° 006-2026-SN/JNJ).
+(2/2) https://t.co/WyjDf7aWB1 — Junta Nacional de Justicia (@JNJPeru) October 9, 2026 Esta jornada contó con la presencia del presidente de la Comisión Permanente de Selección y Nombramiento , Rafael Manuel Ruíz Hidalgo, y de los miembros integrantes Germán Alejandro Julio Serkovic González y Cayo César Galindo Sandoval.
+Lee también: Presidente del Congreso y defensor del Pueblo fortalecen coordinación interinstitucional Como parte de la transparencia del acto, acompañaron el desarrollo de la evaluación un notario público y un representante de la Fiscalía de Prevención del Delito , De este modo, se contribuye a garantizar la imparcialidad y correcta ejecución de esta etapa del proceso.
+La evaluación de conocimientos busca identificar a los postulantes que acrediten los conocimientos requeridos para continuar en el proceso de selección de quien estará a cargo de la jefatura de la ONPE, organismo constitucionalmente autónomo responsable de planificar, organizar y ejecutar los procesos electorales, referéndum y consultas populares.
+Los postulantes que aprueben la evaluación deberán presentar su currículum vitae y la documentación sustentatoria a través de la extranet de la Junta Nacional de Justicia, los días 12 y 13 del presente mes, conforme al cronograma de la Convocatoria n.° 006-2026.
+La JNJ informó que continuará con las siguientes etapas del proceso de selección bajo los principios de mérito, transparencia, igualdad de oportunidades e imparcialidad, con el objetivo de garantizar la elección del profesional más idóneo para ejercer el cargo.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-diez-postulantes-al-cargo-jefe-de-onpe-rindieron-evaluacion-conocimientos-1095359.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Agro Rural interviene 49 puntos críticos para proteger áreas agrícolas en la región Lima</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Los trabajos, que se vienen ejecutando con una inversión de S/ 29.3 millones, protegerán 791 hectáreas de cultivos y beneficiarán a 1,874 familias productoras.
-Estos trabajos incluyen la limpieza, descolmatación y encimado de bordos en 44 kilómetros de cauces de ríos y quebradas, entre ellos las cuencas de los ríos Supe, Chillón y Huaral y la quebrada de Gorgor.
-Asimismo, se interviene en otros sectores ubicados en las provincias de Canta, Cajatambo, Barranca, Oyón, Huarochirí y Yauyos, “donde se han reconocido puntos que requieren atención inmediata”, explicó Agro Rural, en una nota de prensa.
-[Lea también: San Martín: sentencia judicial refuerza la protección de bosques amazónicos ] Trabajos culminados En el marco de las actividades de preparación y respuesta, el director ejecutivo de Agro Rural, Oscar Olivera Cusilayme, inspeccionó los trabajos ejecutados y culminados en los sectores Macas I y Macas II (Santa Rosa de Quives, Canta), verificando en campo las acciones en estos puntos críticos.
-En Macas II, los trabajos finalizaron al 100 % la segunda quincena de setiembre, mientras que, en Macas I culminaron los primeros días de octubre.
-“La intervención comprendió la limpieza y descolmatación de 1,730 metros de cauce y conformación de 3,460 metros de bordos en ambas márgenes del río Chillón”, detalló la institución.
-Estos trabajos benefician a por lo menos 50 familias productoras locales y protegen aproximadamente 100 hectáreas de cultivos, principalmente hortalizas –como col y brócoli– y también maíz.
-“Además, esta es la mejor evidencia de que estamos actuando y dando respuesta de manera efectiva, antes de que llegue la emergencia” por El Niño, aseguró la autoridad del programa del Midagri.
-[Lea también: El Niño: ¿Cómo enfrentaron las antiguas culturas del Perú los impactos de este fenómeno? ] Más intervenciones de Agro Rural Como parte de este recorrido, Olivera Cusilayme también participó en el inicio de dos nuevos servicios de intervención en otros puntos críticos de esta misma región.
-El primero comprende igualmente limpieza, descolmatación y encimado de bordos en diversas zonas de las provincias de Canta, Barranca, Cajatambo y Oyón, labores que se efectuarán con una inversión de S/ 14.09 millones y tendrán un plazo de ejecución de 45 días calendario.
-Al mismo tiempo, comenzaron las intervenciones en sectores como Autisha y Pongo (distrito de Huachupampa), Tambo de Viso (San Mateo), Corcona (Santa Cruz de Cocachacra), entre otros de las provincias de Huarochirí y Yauyos, con una inversión de S/ 5.84 millones y un plazo de 30 días.
-“Nuestra institución continuará ampliando progresivamente su presencia en diversos ámbitos, atendiendo localidades priorizadas ante posibles impactos que podrían comprometer seriamente los medios de vida de los productores familiares”, expresó Olivera.
-Todas estas labores se realizan en cumplimiento del Decreto Supremo N°164-2026-EF que dispone medidas frente a posibles impactos asociados a las intensas precipitaciones por El Niño.
-[Lea también: Fenómeno El Niño: supervisan los trabajos de descolmatación en punto crítico de Lambayeque ] Más en Andina: ?? Los pequeños productores agrarios cuentan con el Seguro Agrícola Catastrófico para afrontar pérdidas ocasionadas por eventos climáticos.
-El Midagri informó que este seguro es gratuito y ofrece una cobertura de hasta S/ 1,000 por hectárea.
-Más información ?? https://t.co/zSIv3qczUr (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 9, 2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-agro-rural-interviene-49-puntos-criticos-para-proteger-areas-agricolas-la-region-lima-1095333.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Presidenta Fujimori participa en entrega de títulos de propiedad en región Lambayeque</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>A dicha zona de la región norteña, la mandataria llegó acompañada por el ministro de Vivienda, Construcción y Saneamiento, Mauricio Arnillas.
-La jefa del Estado personalmente entregó dos títulos de propiedad a las familias beneficiarias ; así como recibió el saludo de la población.
-También acompañan a la presidenta Fujimori, la directora ejecutiva de Cofopri, Cecilia Castro ; así como autoridades municipales y distritales.
-En la ceremonia que se desarrollará en breve, se entregarán más de 2,000 títulos de propiedad .</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-presidenta-fujimori-participa-entrega-titulos-propiedad-region-lambayeque-1095335.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Papa León en Chiclayo: artesanas de Monsefú preparan prendas y recuerdos únicos</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>La artesana monsefuana y embajadora de la Marca Lambayeque, Manuela Ayasta Caicedo, afirmó en diálogo con la agencia Andina que la llegada del sumo pontífice representa una oportunidad histórica para miles de emprendedores de la región, que esperan recibir a visitantes interesados en adquirir productos que expresan la creatividad, historia y las costumbres de los pueblos lambayecanos.
 Durante su participación en la feria artesanal Tradición Viva, inaugurada hoy en la explanada del Banco de la Nación de Chiclayo y que se clausurará mañana sábado, la artesana informó que sus compañeras de Monsefú elaboran estolas, camisas, blusas, mandiles, servilletas bordadas, centros de mesa, tapajarras, bolsos y otros artículos utilitarios, así como gorras alusivas a León XIV.
@@ -1076,57 +1118,27 @@
 Más en Andina: ??Agro Rural interviene 49 puntos críticos para proteger áreas agrícolas en la región Lima https://t.co/toectiMswe https://t.co/N9koO8nE7P (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 9, 2026</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-papa-leon-chiclayo-artesanas-monsefu-preparan-prendas-y-recuerdos-unicos-1095348.aspx</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Senado: Comisión de Constitución sesiona hoy para debatir facultades legislativas</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Con ese propósito, el presidente de dicha comisión, Carlos Mesía Ramírez (Fuerza Popular) citó mediante un oficio a los miembros titulares y suplentes de dicho grupo de trabajo para que asistan a esta reunión que se realizará en la sala Miguel Grau, del Palacio Legislativo.
-Lee también: Presidenta entregó títulos en Lambayeque y dijo que brindan seguridad jurídica a familias La sesión será la continuación de la reunión convocada el viernes y en la que se presentó el presidente del Consejo de Ministros, Luis Galarreta , y los ministros de Desarrollo Agrario y Riego, Marco Vinelli, y de la Producción, Juan Carlos Requejo.
-El titular de la Presidencia del Consejo de Ministros (PCM) reiteró durante su presentación en la necesidad de que el Congreso otorgue mayores facultades legislativas que las aprobadas en la propuesta legislativa de la Cámara Baja, mediante la cual se otorga facultades al Ejecutivo en materias de seguridad ciudadana y fenómeno El Niño por un periodo de 90 días.
-De acuerdo con el premier Galarreta son insuficientes las facultades aprobadas en la Cámara de Diputados, incluso en materia de seguridad ciudadana y fenómeno El Niño, ya que en cuanto a seguridad se requiere una mayor inteligencia operativa para combatir a las bandas criminales.
-Al término de esta sesión, el presidente de la Comisión de Constitución, señaló que están pendientes la presentación de los ministros de Justicia y Derechos Humanos , Ernesto Álvarez, y de Vivienda, Construcción y Saneamiento , Mauricio Arnillas.
-De este modo, el Senado continuará con el debate de las facultades legislativas planteadas por el Ejecutivo el 29 de agosto pasado y que la Cámara de Diputados aprobó solo 20 de los 66 puntos planteados inicialmente.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-senado-comision-constitucion-sesiona-hoy-para-debatir-facultades-legislativas-1095346.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>ONPE entrega actas observadas de Lima Metropolitana a los JEE para su resolución</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>De acuerdo con la plataforma oficial de resultados electorales , a las 18:00 horas de hoy, son 1,886 actas observadas , que representan el 7.157 % de las actas procesadas de Lima Metropolitana, correspondientes a las Elecciones Regionales y Municipales 2026.
 Las 28 Oficinas Descentralizadas de Procesos Electorales (ODPE) que operaron en Lima Metropolitana enviaron las actas de sus respectivas circunscripciones a los 10 JEE correspondientes para administrar justicia en primera instancia en la capital.
@@ -1139,39 +1151,9 @@
 En el caso de las firmas, al menos una de las actas debe contar con la firma de los tres miembros de mesa y las otras dos, con las firmas de dos miembros de mesa.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-onpe-entrega-actas-observadas-lima-metropolitana-a-los-jee-para-su-resolucion-1095349.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>46304</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Diez postulantes al cargo de jefe de la ONPE rindieron evaluación de conocimientos</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>?? ? Imágenes de los momentos previos al examen de conocimientos del concurso público para la selección y nombramiento del jefe de la ONPE (convocatoria n.° 006-2026-SN/JNJ).
-(2/2) https://t.co/WyjDf7aWB1 — Junta Nacional de Justicia (@JNJPeru) October 9, 2026 Esta jornada contó con la presencia del presidente de la Comisión Permanente de Selección y Nombramiento , Rafael Manuel Ruíz Hidalgo, y de los miembros integrantes Germán Alejandro Julio Serkovic González y Cayo César Galindo Sandoval.
-Lee también: Presidente del Congreso y defensor del Pueblo fortalecen coordinación interinstitucional Como parte de la transparencia del acto, acompañaron el desarrollo de la evaluación un notario público y un representante de la Fiscalía de Prevención del Delito , De este modo, se contribuye a garantizar la imparcialidad y correcta ejecución de esta etapa del proceso.
-La evaluación de conocimientos busca identificar a los postulantes que acrediten los conocimientos requeridos para continuar en el proceso de selección de quien estará a cargo de la jefatura de la ONPE, organismo constitucionalmente autónomo responsable de planificar, organizar y ejecutar los procesos electorales, referéndum y consultas populares.
-Los postulantes que aprueben la evaluación deberán presentar su currículum vitae y la documentación sustentatoria a través de la extranet de la Junta Nacional de Justicia, los días 12 y 13 del presente mes, conforme al cronograma de la Convocatoria n.° 006-2026.
-La JNJ informó que continuará con las siguientes etapas del proceso de selección bajo los principios de mérito, transparencia, igualdad de oportunidades e imparcialidad, con el objetivo de garantizar la elección del profesional más idóneo para ejercer el cargo.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-diez-postulantes-al-cargo-jefe-de-onpe-rindieron-evaluacion-conocimientos-1095359.aspx</t>
         </is>
       </c>
     </row>
